--- a/ECCV2026_后续200篇论文汇总_01-200.xlsx
+++ b/ECCV2026_后续200篇论文汇总_01-200.xlsx
@@ -456,7 +456,7 @@
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>数据特殊处理
-（有/无/未说明）</t>
+（有/无）</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1707,7 +1707,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -7112,7 +7112,7 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -7935,7 +7935,7 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>未说明</t>
+          <t>无</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
